--- a/Assets/ReSurvivor2/MasterDataExcels/MasterMission.xlsx
+++ b/Assets/ReSurvivor2/MasterDataExcels/MasterMission.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alfam\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC7C378B-68D9-4027-8530-D373914C01CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92292EFE-E64B-401C-9117-E026077121BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{F568E1A9-666B-4DF7-A1D7-8B595FE1F36C}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
   <si>
     <t>Minute</t>
     <phoneticPr fontId="1"/>
@@ -35,45 +35,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Stage4Computer</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>StartComputerName</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Stage0Computer</t>
-  </si>
-  <si>
-    <t>Stage0Computer</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Stage4Computer</t>
-  </si>
-  <si>
     <t>ComputerName</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Stage1Computer</t>
-  </si>
-  <si>
-    <t>Stage2Computer</t>
-  </si>
-  <si>
-    <t>Stage3Computer</t>
-  </si>
-  <si>
-    <t>Stage5Computer</t>
-  </si>
-  <si>
     <t>MissionName</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>EndComputerName</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -131,6 +97,47 @@
   </si>
   <si>
     <t>メールのメインメッセージ2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>StartComputerStageNumber</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EndComputerStageNumber</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Stage0</t>
+  </si>
+  <si>
+    <t>Stage0</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Stage1</t>
+  </si>
+  <si>
+    <t>Stage1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Stage2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Stage3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Stage4</t>
+  </si>
+  <si>
+    <t>Stage4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Stage5</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -538,8 +545,8 @@
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" customWidth="1"/>
+    <col min="2" max="2" width="27.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.75" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="28.375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="26.5" bestFit="1" customWidth="1"/>
@@ -548,13 +555,13 @@
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -563,13 +570,13 @@
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.4">
@@ -577,10 +584,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D2">
         <v>10</v>
@@ -589,13 +596,13 @@
         <v>30</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.4">
@@ -603,10 +610,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D3">
         <v>5</v>
@@ -615,13 +622,13 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.4">
@@ -629,10 +636,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D4">
         <v>4</v>
@@ -641,48 +648,48 @@
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="J16" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="10:10" x14ac:dyDescent="0.4">
       <c r="J17" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="10:10" x14ac:dyDescent="0.4">
       <c r="J18" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="10:10" x14ac:dyDescent="0.4">
       <c r="J19" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="10:10" x14ac:dyDescent="0.4">
       <c r="J20" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.4">
       <c r="J21" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="10:10" x14ac:dyDescent="0.4">
       <c r="J22" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
